--- a/EXCEL/Exercise Files/Chapter05/05_02_SingleCovariance.xlsx
+++ b/EXCEL/Exercise Files/Chapter05/05_02_SingleCovariance.xlsx
@@ -1,24 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Curtis\Desktop\Exercise Files\Chapter05\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE11DC3-C703-43B2-B707-91D65E1A5ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C163E6E0-BDF4-4D08-A66F-90BAF0BE8422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="288" yWindow="324" windowWidth="22752" windowHeight="11916" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -60,12 +69,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -80,12 +95,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -421,15 +437,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="10.69140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.69140625" customWidth="1"/>
-    <col min="5" max="5" width="18.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.6640625" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -440,87 +456,137 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
+      <c r="C2">
+        <f>(A2-AVERAGE($A$2:$A$11))*(B2-AVERAGE($B$2:$B$11))</f>
+        <v>4.6799999999999988</v>
+      </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>4</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C3">
+        <f t="shared" ref="C3:C11" si="0">(A3-AVERAGE($A$2:$A$11))*(B3-AVERAGE($B$2:$B$11))</f>
+        <v>1.379999999999999</v>
+      </c>
+      <c r="E3">
+        <f>_xlfn.COVARIANCE.P(A2:A11,B2:B11)</f>
+        <v>-0.47999999999999987</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>7</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>-7.9200000000000008</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>0.77999999999999947</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>-7.5199999999999987</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>0.68000000000000071</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>8</v>
       </c>
       <c r="B8">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>12.580000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>1.0799999999999992</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>6</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>-0.41999999999999987</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11">
         <v>2</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>-10.119999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f>SUM(C2:C11)</f>
+        <v>-4.7999999999999989</v>
       </c>
     </row>
   </sheetData>
